--- a/informes/bajas_laliga_2026-09-17.xlsx
+++ b/informes/bajas_laliga_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,27 +458,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sistema (Prueba)</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Verificación de carpetas</t>
+          <t>Militão</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Física / Médica</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Activo</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El script funciona pero la web requiere revisión de HTML.</t>
+          <t>Rotura Ligamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gavi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Duda</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Molestias</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Atlético de Madrid</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Koke</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Disciplinaria (Sanción)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cinco Amarillas</t>
         </is>
       </c>
     </row>

--- a/informes/bajas_laliga_2026-09-17.xlsx
+++ b/informes/bajas_laliga_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,81 +458,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Militão</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rotura Ligamento</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FC Barcelona</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Gavi</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Duda</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Molestias</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Atlético de Madrid</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Koke</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Disciplinaria (Sanción)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Cinco Amarillas</t>
+          <t>API no devolvió registros</t>
         </is>
       </c>
     </row>

--- a/informes/bajas_laliga_2026-09-17.xlsx
+++ b/informes/bajas_laliga_2026-09-17.xlsx
@@ -458,27 +458,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>API no devolvió registros</t>
+          <t>Todos los planteles limpios</t>
         </is>
       </c>
     </row>

--- a/informes/bajas_laliga_2026-09-17.xlsx
+++ b/informes/bajas_laliga_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,27 +458,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sin bajas</t>
+          <t>Atlético de Madrid</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Thomas Lemar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Física / Médica</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Duda</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Todos los planteles limpios</t>
+          <t>Molestias físicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Andreas Christensen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Baja (Lesión)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Tendinopatía aquilea</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Éder Militão</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Baja (Lesión)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Rotura de ligamento</t>
         </is>
       </c>
     </row>

--- a/informes/bajas_laliga_2026-09-17.xlsx
+++ b/informes/bajas_laliga_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Atlético de Madrid</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thomas Lemar</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,24 +473,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Molestias físicas</t>
+          <t>Molestias en el pubis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Andreas Christensen</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,39 +500,201 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Baja (Lesión)</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tendinopatía aquilea</t>
+          <t>Operado de la muñeca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Atlético de Madrid</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pablo Barrios</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Lesión muscular en la pierna</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dani Olmo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Lesión en el bíceps femoral</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fermín López</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Lesión en el recto anterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Marc Bernal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Rotura de ligamento cruzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Éder Militão</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Baja (Lesión)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Rotura de ligamento</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dani Ceballos</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Esguince de tobillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Eduardo Camavinga</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Esguince de rodilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hamari Traoré</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Rotura de ligamento cruzado</t>
         </is>
       </c>
     </row>

--- a/informes/bajas_laliga_2026-09-17.xlsx
+++ b/informes/bajas_laliga_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Abqar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,19 +478,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Molestias en el pubis</t>
+          <t>Molestias físicas</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Aitor Mañas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,19 +505,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Operado de la muñeca</t>
+          <t>Parte médico oficial pendiente</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atlético de Madrid</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,19 +532,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lesión muscular en la pierna</t>
+          <t>Molestias en el pubis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dani Olmo</t>
+          <t>Dani Vivian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,19 +559,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lesión en el bíceps femoral</t>
+          <t>Lesión en el aductor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fermín López</t>
+          <t>Unai Egiluz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -586,19 +586,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lesión en el recto anterior</t>
+          <t>Rotura de ligamento cruzado anterior</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -613,19 +613,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rotura de ligamento cruzado</t>
+          <t>Operado de la muñeca</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atlético de Madrid</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dani Ceballos</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -640,19 +640,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esguince de tobillo</t>
+          <t>Lesión muscular en el sóleo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eduardo Camavinga</t>
+          <t>Antañón</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -667,34 +667,844 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Esguince de rodilla</t>
+          <t>Lesión muscular</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Iago Aspas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Problemas físicos confirmados</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Deportivo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Angeliño</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Disciplinaria (Sanción)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tarjeta roja directa</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gorosabel</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Problemas físicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Javi Puado</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Molestias musculares</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jofre</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Esguince leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kike García</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Baja de larga duración hasta 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Omar El Hilali</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Disciplinaria (Sanción)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tarjeta roja directa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dani Olmo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Lesión en el bíceps femoral</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fermín López</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Lesión en el recto anterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Frenkie de Jong</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Lesión grave de rodilla (Baja hasta 2027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Joan García</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Duda</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Leves molestias en la rodilla derecha</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Marc Bernal</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Rotura de ligamento cruzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Juanmi Jiménez</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Dolencias musculares</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kiko Femenía</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sobrecarga</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Uche</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lesión grave (Baja para toda la temporada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Aimar Oroz</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Molestias en el muslo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Herrando</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Esguince de tobillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Moi Gómez</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Lesión fibrilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Valentín Rosier</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Problemas musculares</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aitor Ruibal</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Lesión muscular en el aductor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dani Ceballos</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Esguince de tobillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Eduardo Camavinga</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Esguince de rodilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ferland Mendy</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Molestias musculares</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Rodrygo Goes</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Trabajo específico en el gimnasio</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Éder Militão</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Proceso de recuperación muscular</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Real Sociedad</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Hamari Traoré</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>Rotura de ligamento cruzado</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Odriozola</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Problemas físicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kike Salas</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Contusión (Trabajo específico)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lucas Stassin</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Lesión miofascial en el aductor largo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Rubén Vargas</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Esguince de tobillo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sangante</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Física / Médica</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Molestias en la rodilla</t>
         </is>
       </c>
     </row>

--- a/informes/bajas_laliga_2026-09-17.xlsx
+++ b/informes/bajas_laliga_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abqar</t>
+          <t>Hugo Novoa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Molestias físicas</t>
+          <t>Molestias en el pubis</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Abqar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molestias en el pubis</t>
+          <t>Molestias físicas</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dani Vivian</t>
+          <t>Unai Simón</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lesión en el aductor</t>
+          <t>Operado de la muñeca</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unai Egiluz</t>
+          <t>Dani Vivian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotura de ligamento cruzado anterior</t>
+          <t>Lesión en el aductor</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Unai Egiluz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Operado de la muñeca</t>
+          <t>Rotura de ligamento cruzado anterior</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Antañón</t>
+          <t>Iago Aspas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lesión muscular</t>
+          <t>Problemas físicos confirmados</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Antañón</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Problemas físicos confirmados</t>
+          <t>Lesión muscular</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gorosabel</t>
+          <t>Javi Puado</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Problemas físicos</t>
+          <t>Molestias musculares</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Javi Puado</t>
+          <t>Kike García</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Molestias musculares</t>
+          <t>Baja de larga duración hasta 2027</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jofre</t>
+          <t>Gorosabel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esguince leve</t>
+          <t>Problemas físicos</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Jofre</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Baja de larga duración hasta 2027</t>
+          <t>Esguince leve</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frenkie de Jong</t>
+          <t>Marc Bernal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lesión grave de rodilla (Baja hasta 2027)</t>
+          <t>Rotura de ligamento cruzado</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Joan García</t>
+          <t>Frenkie de Jong</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Leves molestias en la rodilla derecha</t>
+          <t>Lesión grave de rodilla (Baja hasta 2027)</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Joan García</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Duda</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rotura de ligamento cruzado</t>
+          <t>Leves molestias en la rodilla derecha</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Juanmi Jiménez</t>
+          <t>Uche</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dolencias musculares</t>
+          <t>Lesión grave (Baja para toda la temporada)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>Juanmi Jiménez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sobrecarga</t>
+          <t>Dolencias musculares</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Uche</t>
+          <t>Kiko Femenía</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lesión grave (Baja para toda la temporada)</t>
+          <t>Sobrecarga</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Valentín Rosier</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Molestias en el muslo</t>
+          <t>Problemas musculares</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Herrando</t>
+          <t>Aimar Oroz</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Esguince de tobillo</t>
+          <t>Molestias en el muslo</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Herrando</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lesión fibrilar</t>
+          <t>Esguince de tobillo</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Valentín Rosier</t>
+          <t>Moi Gómez</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Problemas musculares</t>
+          <t>Lesión fibrilar</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dani Ceballos</t>
+          <t>Eduardo Camavinga</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Esguince de tobillo</t>
+          <t>Esguince de rodilla</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Eduardo Camavinga</t>
+          <t>Dani Ceballos</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Esguince de rodilla</t>
+          <t>Esguince de tobillo</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ferland Mendy</t>
+          <t>Éder Militão</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Molestias musculares</t>
+          <t>Proceso de recuperación muscular</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Éder Militão</t>
+          <t>Ferland Mendy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Proceso de recuperación muscular</t>
+          <t>Molestias musculares</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kike Salas</t>
+          <t>Lucas Stassin</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Contusión (Trabajo específico)</t>
+          <t>Lesión miofascial en el aductor largo</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lucas Stassin</t>
+          <t>Kike Salas</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lesión miofascial en el aductor largo</t>
+          <t>Contusión (Trabajo específico)</t>
         </is>
       </c>
     </row>
@@ -1505,6 +1505,222 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>Molestias en la rodilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sin bajas reportadas</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Plantilla limpia</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sin bajas reportadas</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Plantilla limpia</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sin bajas reportadas</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Plantilla limpia</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sin bajas reportadas</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Plantilla limpia</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sin bajas reportadas</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Plantilla limpia</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sin bajas reportadas</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Plantilla limpia</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sin bajas reportadas</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Plantilla limpia</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sin bajas reportadas</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Disponible</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Plantilla limpia</t>
         </is>
       </c>
     </row>

--- a/informes/bajas_laliga_2026-09-17.xlsx
+++ b/informes/bajas_laliga_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hugo Novoa</t>
+          <t>Facundo Garcés</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Molestias en el pubis</t>
+          <t>Rotura de ligamento cruzado. Baja indefinida.</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aitor Mañas</t>
+          <t>Benavídez Protesoni</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Parte médico oficial pendiente</t>
+          <t>Molestias. Baja esta jornada.</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abqar</t>
+          <t>Mikel Rodríguez</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -532,19 +532,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molestias físicas</t>
+          <t>Rotura de ligamento cruzado. Baja hasta Abril.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unai Simón</t>
+          <t>Aitor Mañas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Operado de la muñeca</t>
+          <t>Traumatismo craneoencefálico. Baja esta jornada.</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dani Vivian</t>
+          <t>Daniel Vivian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lesión en el aductor</t>
+          <t>Lesión en el aductor. Baja hasta Octubre.</t>
         </is>
       </c>
     </row>
@@ -613,19 +613,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rotura de ligamento cruzado anterior</t>
+          <t>Rotura de ligamento cruzado. Baja hasta Enero.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Atlético de Madrid</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pablo Barrios</t>
+          <t>Peio Canales</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -640,19 +640,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lesión muscular en el sóleo</t>
+          <t>Lesión en el sóleo. Baja esta jornada.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Iago Aspas</t>
+          <t>Selton Sánchez</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -667,19 +667,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Problemas físicos confirmados</t>
+          <t>No convocado. Baja esta jornada.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Antañón</t>
+          <t>Asier Hierro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -694,24 +694,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lesión muscular</t>
+          <t>No convocado. Baja esta jornada.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Atlético de Madrid</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Angeliño</t>
+          <t>Pablo Barrios</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Disciplinaria (Sanción)</t>
+          <t>Física / Médica</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -721,19 +721,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tarjeta roja directa</t>
+          <t>Lesión en el sóleo. Baja esta jornada.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Atlético de Madrid</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Javi Puado</t>
+          <t>Julián Álvarez</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -748,19 +748,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Molestias musculares</t>
+          <t>Sobrecarga. Baja esta jornada.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Atlético de Madrid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kike García</t>
+          <t>Alexander Sørloth</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -775,19 +775,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Baja de larga duración hasta 2027</t>
+          <t>Contractura muscular. Baja esta jornada.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gorosabel</t>
+          <t>Joan García</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -802,19 +802,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Problemas físicos</t>
+          <t>Molestias. Baja hasta finales de Septiembre.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jofre</t>
+          <t>Frenkie de Jong</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -829,24 +829,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Esguince leve</t>
+          <t>Lesión de rodilla. Baja hasta Noviembre.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Omar El Hilali</t>
+          <t>Bardghji</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Disciplinaria (Sanción)</t>
+          <t>Física / Médica</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tarjeta roja directa</t>
+          <t>Rotura de ligamento cruzado. Baja hasta Marzo.</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dani Olmo</t>
+          <t>Bisiwu</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -883,196 +883,196 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lesión en el bíceps femoral</t>
+          <t>Parte médico oficial en revisión.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fermín López</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lesión en el recto anterior</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marc Bernal</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotura de ligamento cruzado</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Frenkie de Jong</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lesión grave de rodilla (Baja hasta 2027)</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Joan García</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Leves molestias en la rodilla derecha</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Uche</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lesión grave (Baja para toda la temporada)</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Juanmi Jiménez</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dolencias musculares</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kiko Femenía</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sobrecarga</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
@@ -1084,643 +1084,238 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Valentín Rosier</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Problemas musculares</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aimar Oroz</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Molestias en el muslo</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Herrando</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Esguince de tobillo</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Moi Gómez</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lesión fibrilar</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aitor Ruibal</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lesión muscular en el aductor</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Eduardo Camavinga</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Esguince de rodilla</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dani Ceballos</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Esguince de tobillo</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Éder Militão</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Proceso de recuperación muscular</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rodrygo Goes</t>
+          <t>Sin bajas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Física / Médica</t>
+          <t>Ninguna</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Disponible</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trabajo específico en el gimnasio</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Ferland Mendy</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Molestias musculares</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Hamari Traoré</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Rotura de ligamento cruzado</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Odriozola</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Problemas físicos</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Sevilla FC</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Lucas Stassin</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Lesión miofascial en el aductor largo</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Sevilla FC</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Kike Salas</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Contusión (Trabajo específico)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Sevilla FC</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Rubén Vargas</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Esguince de tobillo</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Sevilla FC</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Sangante</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Física / Médica</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Molestias en la rodilla</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Sin bajas reportadas</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Plantilla limpia</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Sin bajas reportadas</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Plantilla limpia</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Leganés</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Sin bajas reportadas</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Plantilla limpia</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Sin bajas reportadas</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Plantilla limpia</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Sin bajas reportadas</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Plantilla limpia</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Sin bajas reportadas</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Plantilla limpia</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Sin bajas reportadas</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Plantilla limpia</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Villarreal</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Sin bajas reportadas</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Disponible</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Plantilla limpia</t>
+          <t>Plantilla limpia y lista para la jornada.</t>
         </is>
       </c>
     </row>
